--- a/resources/templates/standard/L1100-13.xlsx
+++ b/resources/templates/standard/L1100-13.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>월별 중점 점검 테마</t>
   </si>
@@ -790,7 +793,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="35.25" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -869,7 +874,7 @@
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -897,44 +902,44 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
       <c r="M5" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
@@ -999,7 +1004,7 @@
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -1009,7 +1014,7 @@
       <c r="G8" s="19"/>
       <c r="H8" s="20"/>
       <c r="I8" s="21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" s="21"/>
       <c r="K8" s="21"/>
@@ -1029,7 +1034,7 @@
     </row>
     <row r="9" ht="41.15" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
@@ -1057,7 +1062,7 @@
     </row>
     <row r="10" ht="41.15" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
@@ -1085,7 +1090,7 @@
     </row>
     <row r="11" ht="41.15" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
@@ -1113,7 +1118,7 @@
     </row>
     <row r="12" ht="41.15" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -1141,7 +1146,7 @@
     </row>
     <row r="13" ht="41.15" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
@@ -1169,7 +1174,7 @@
     </row>
     <row r="14" ht="41.15" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="30"/>
       <c r="C14" s="30"/>
@@ -1398,19 +1403,19 @@
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
       <c r="T22" s="33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U22" s="34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V22" s="34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W22" s="34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X22" s="34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" ht="20.15" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
